--- a/CodeSystem-ACCESSUnalignmentResultCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentResultCS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>Level</t>
@@ -160,6 +160,15 @@
   </si>
   <si>
     <t>Additional review is needed and you will receive further information once the manual review of the unalignment request is complete.</t>
+  </si>
+  <si>
+    <t>patient-not-aligned</t>
+  </si>
+  <si>
+    <t>Patient not aligned</t>
+  </si>
+  <si>
+    <t>Patient is not currently aligned to this participant in the specified track and therefore cannot be unaligned.</t>
   </si>
 </sst>
 </file>
@@ -471,7 +480,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -516,6 +525,20 @@
         <v>48</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CodeSystem-ACCESSUnalignmentResultCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentResultCS.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/CodeSystem/ACCESSUnalignmentResultCS</t>
+    <t>https://dsacms.github.io/cmmi-access-model/CodeSystem/ACCESSUnalignmentResultCS</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSUnalignmentResultCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentResultCS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>Level</t>
@@ -169,6 +169,15 @@
   </si>
   <si>
     <t>Patient is not currently aligned to this participant in the specified track and therefore cannot be unaligned.</t>
+  </si>
+  <si>
+    <t>cannot-unalign-during-lock-in</t>
+  </si>
+  <si>
+    <t>Cannot unalign during lock-in</t>
+  </si>
+  <si>
+    <t>Patient is within the 90-day lock-in period and cannot be unaligned.</t>
   </si>
 </sst>
 </file>
@@ -480,7 +489,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -539,6 +548,20 @@
         <v>51</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CodeSystem-ACCESSUnalignmentResultCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentResultCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSUnalignmentResultCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentResultCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSUnalignmentResultCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentResultCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSUnalignmentResultCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentResultCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSUnalignmentResultCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentResultCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
